--- a/Data_clean/MCAS/Estados_US/Edos_USA_2024/MASSACHUSETTS_2024.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2024/MASSACHUSETTS_2024.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -439,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C8">
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Benemérito de las Américas</t>
+          <t>Benemérito De Las Américas</t>
         </is>
       </c>
       <c r="C12">
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Chapultenango</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -613,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C19">
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -678,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -691,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -704,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -717,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -730,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -743,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>La Independencia</t>
@@ -756,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -769,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -782,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -795,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C33">
@@ -808,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -821,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Mitontic</t>
@@ -834,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -847,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -860,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -873,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Oxchuc</t>
@@ -886,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -899,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Pantelhó</t>
@@ -912,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -925,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -938,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Pueblo Nuevo Solistahuacán</t>
@@ -951,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C45">
@@ -964,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>San Juan Cancuc</t>
@@ -977,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -990,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Simojovel</t>
@@ -1003,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Sitalá</t>
@@ -1016,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Socoltenango</t>
@@ -1029,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -1042,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -1055,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -1068,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -1081,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tumbalá</t>
@@ -1094,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -1107,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -1120,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tzimol</t>
@@ -1133,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -1146,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1159,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Zinacantán</t>
@@ -1172,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C62">
@@ -1203,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Praxedis G. Guerrero</t>
@@ -1216,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C65">
@@ -1231,7 +1531,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1247,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1260,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1273,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1286,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1299,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1312,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1325,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1338,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1351,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1364,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1377,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Álvaro Obregón</t>
@@ -1390,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C78">
@@ -1405,7 +1765,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Coahuila de Zaragoza</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1421,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C80">
@@ -1452,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1465,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C83">
@@ -1496,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1509,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1522,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C87">
@@ -1537,12 +1927,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C88">
@@ -1553,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1566,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1579,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1592,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Cuautitlán Izcalli</t>
@@ -1605,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C93">
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1631,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C95">
@@ -1644,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1657,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C97">
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1683,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C99">
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1709,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1722,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C102">
@@ -1735,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1748,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tonatico</t>
@@ -1761,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1774,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Villa del Carbón</t>
+          <t>Villa Del Carbón</t>
         </is>
       </c>
       <c r="C106">
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Zumpango</t>
@@ -1800,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C108">
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1844,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -1857,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>León</t>
@@ -1870,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1896,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C115">
@@ -1916,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C116">
@@ -1927,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1940,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -1953,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1966,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Atlamajalcingo del Monte</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C120">
@@ -1979,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -1992,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C122">
@@ -2005,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C123">
@@ -2018,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -2031,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2044,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C126">
@@ -2057,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -2070,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C128">
@@ -2083,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2096,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -2109,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -2122,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2135,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2148,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -2161,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C135">
@@ -2174,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C136">
@@ -2187,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C137">
@@ -2200,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -2213,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -2226,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C140">
@@ -2257,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -2270,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -2283,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Huasca de Ocampo</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C144">
@@ -2296,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2309,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -2322,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C147">
@@ -2335,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2348,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C149">
@@ -2379,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C151">
@@ -2392,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -2405,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -2418,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C154">
@@ -2431,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2444,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -2457,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -2470,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2483,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C159">
@@ -2496,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -2509,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -2522,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C162">
@@ -2535,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C163">
@@ -2548,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C164">
@@ -2561,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tuxcacuesco</t>
@@ -2574,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tuxcueca</t>
@@ -2587,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C167">
@@ -2600,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2613,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C169">
@@ -2628,7 +3403,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Michoacán de Ocampo</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2644,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -2657,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Chinicuila</t>
@@ -2670,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Coahuayana</t>
@@ -2683,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2696,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2709,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -2722,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2735,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2748,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -2761,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -2774,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -2787,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -2800,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C183">
@@ -2813,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2826,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -2839,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2852,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2865,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C188">
@@ -2896,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C190">
@@ -2909,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C191">
@@ -2922,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C192">
@@ -2953,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -2966,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C195">
@@ -2997,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C197">
@@ -3010,9 +3905,14 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C198">
@@ -3041,9 +3941,14 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C200">
@@ -3054,9 +3959,14 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Huajuapan de León</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C201">
@@ -3067,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -3080,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C203">
@@ -3093,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -3106,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -3119,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>San Andrés Cabecera Nueva</t>
@@ -3132,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -3145,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>San Dionisio del Mar</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C208">
@@ -3158,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>San Jerónimo Sosola</t>
@@ -3171,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3184,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>San Juan Teitipac</t>
@@ -3197,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>San Pedro Yólox</t>
@@ -3210,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Santa Catarina Yosonotú</t>
@@ -3223,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -3236,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -3249,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -3262,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -3275,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -3288,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -3301,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C220">
@@ -3314,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C221">
@@ -3327,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C222">
@@ -3358,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Acatzingo</t>
@@ -3371,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Amixtlán</t>
@@ -3384,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -3397,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Cañada Morelos</t>
@@ -3410,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -3423,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -3436,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -3449,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -3462,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -3475,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -3488,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -3501,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -3514,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -3527,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -3540,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C238">
@@ -3553,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -3566,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Lafragua</t>
@@ -3579,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -3592,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -3605,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -3618,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3631,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>San Felipe Teotlalcingo</t>
@@ -3644,9 +4769,14 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C246">
@@ -3657,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -3670,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -3683,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -3696,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -3709,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -3722,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -3735,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -3748,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -3761,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -3774,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -3787,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -3800,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -3813,9 +5003,14 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C259">
@@ -3844,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -3857,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -3870,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C263">
@@ -3901,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C265">
@@ -3932,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -3945,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3958,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C269">
@@ -3971,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C270">
@@ -3984,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C271">
@@ -4015,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -4028,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -4041,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C275">
@@ -4072,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -4085,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -4098,9 +5363,14 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C279">
@@ -4129,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -4142,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -4155,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -4168,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -4181,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C285">
@@ -4212,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -4225,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>González</t>
@@ -4238,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -4251,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -4264,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C291">
@@ -4295,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C293">
@@ -4308,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C294">
@@ -4321,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -4334,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Santa Isabel Xiloxoxtla</t>
@@ -4347,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -4360,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C298">
@@ -4375,7 +5725,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Veracruz de Ignacio de la Llave</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4391,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -4404,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -4417,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -4430,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -4443,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Cerro Azul</t>
@@ -4456,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Chicontepec</t>
@@ -4469,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -4482,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4495,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C308">
@@ -4508,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Ilamatlán</t>
@@ -4521,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -4534,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -4547,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -4560,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -4573,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -4586,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -4599,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -4612,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -4625,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -4638,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -4651,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Texcatepec</t>
@@ -4664,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -4677,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -4690,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Villa Aldama</t>
@@ -4703,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -4716,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -4729,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -4742,9 +6227,14 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C327">
@@ -4773,9 +6263,14 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C329">
@@ -4804,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -4817,9 +6317,14 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C332">
@@ -4832,7 +6337,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C333">
@@ -4840,41 +6345,6 @@
       </c>
       <c r="D333">
         <v>1</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 808,027</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Junio de 2025</t>
-        </is>
       </c>
     </row>
   </sheetData>
